--- a/Predictions/2026-04-18.xlsx
+++ b/Predictions/2026-04-18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD747313-F40F-40A0-B604-769C1329CF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D82FEAA-F3A0-4FF3-AE8E-8D985AD40AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -314,40 +314,46 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -672,23 +678,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="6" t="s">
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="7"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -697,10 +703,10 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -712,13 +718,13 @@
       <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -727,10 +733,10 @@
       <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
@@ -741,10 +747,10 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3">
@@ -756,25 +762,25 @@
       <c r="G3" s="3">
         <v>0.41779646230124612</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="16">
         <v>0.41779646230124612</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="16">
         <v>0.4000846590633545</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="17">
         <v>0.1821188786353993</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="12">
         <v>0.58507962712671024</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="8">
         <v>0.53724954619042453</v>
       </c>
     </row>
@@ -785,10 +791,10 @@
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="3">
@@ -800,25 +806,25 @@
       <c r="G4" s="3">
         <v>0.57002409575526458</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="16">
         <v>0.57002409575526458</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="16">
         <v>0.25844769102402221</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="17">
         <v>0.17152821322071329</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="12">
         <v>0.55236031228573046</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="8">
         <v>0.56008091750145383</v>
       </c>
     </row>
@@ -829,10 +835,10 @@
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="3">
@@ -844,25 +850,25 @@
       <c r="G5" s="3">
         <v>0.48455759982842</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="16">
         <v>0.41147603968855212</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="16">
         <v>0.48455759982842</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="17">
         <v>0.1039663604830279</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="12">
         <v>0.57726191012009487</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="8">
         <v>0.58823704302014712</v>
       </c>
     </row>
@@ -873,10 +879,10 @@
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3">
@@ -888,25 +894,25 @@
       <c r="G6" s="3">
         <v>0.5787481150693905</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="16">
         <v>0.5787481150693905</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="16">
         <v>0.26650029803927933</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="17">
         <v>0.15475158689133031</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="12">
         <v>0.54153527244196309</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="8">
         <v>0.52246509063124191</v>
       </c>
     </row>
@@ -917,10 +923,10 @@
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="3">
@@ -932,25 +938,25 @@
       <c r="G7" s="3">
         <v>0.53965320878892376</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="16">
         <v>0.53965320878892376</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="16">
         <v>0.16154110435959401</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="17">
         <v>0.29880568685148229</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="12">
         <v>0.5206442695273158</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="8">
         <v>0.66567702703587706</v>
       </c>
     </row>
@@ -961,10 +967,10 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="3">
@@ -976,25 +982,25 @@
       <c r="G8" s="3">
         <v>0.46807533244096289</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="16">
         <v>0.46807533244096289</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="16">
         <v>0.39081062829674401</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="17">
         <v>0.14111403926229321</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="12">
         <v>0.57036701856795147</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="8">
         <v>0.64140582314118721</v>
       </c>
     </row>
@@ -1005,10 +1011,10 @@
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="3">
@@ -1020,25 +1026,25 @@
       <c r="G9" s="3">
         <v>0.54386814242205095</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="16">
         <v>0.54386814242205095</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="16">
         <v>0.34725872550447062</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="17">
         <v>0.1088731320734785</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="12">
         <v>0.55213357416946263</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="8">
         <v>0.5063976391063858</v>
       </c>
     </row>
@@ -1049,10 +1055,10 @@
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="3">
@@ -1064,25 +1070,25 @@
       <c r="G10" s="3">
         <v>0.66479288740316855</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="16">
         <v>0.66479288740316855</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="16">
         <v>0.19650377027372881</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="17">
         <v>0.1387033423231028</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="12">
         <v>0.61800500937999048</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="8">
         <v>0.74145832088746899</v>
       </c>
     </row>
@@ -1093,10 +1099,10 @@
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="3">
@@ -1108,25 +1114,25 @@
       <c r="G11" s="3">
         <v>0.67285247674920923</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="16">
         <v>0.67285247674920923</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="16">
         <v>0.16801189657963531</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="17">
         <v>0.15913562667115561</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="12">
         <v>0.56495442307833654</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="8">
         <v>0.51582762236944391</v>
       </c>
     </row>
@@ -1137,10 +1143,10 @@
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="3">
@@ -1152,25 +1158,25 @@
       <c r="G12" s="3">
         <v>0.55407562634678231</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="16">
         <v>0.55407562634678231</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="16">
         <v>0.1870284866100306</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="17">
         <v>0.25889588704318711</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="12">
         <v>0.55532067109467609</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="8">
         <v>0.68077962743839049</v>
       </c>
     </row>

--- a/Predictions/2026-04-18.xlsx
+++ b/Predictions/2026-04-18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D82FEAA-F3A0-4FF3-AE8E-8D985AD40AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFF11CE-8840-4C95-9FD7-C7F793E31535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,13 +179,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -303,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -332,15 +325,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -349,12 +337,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -658,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -678,23 +660,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="13" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="13" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="15"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -706,7 +688,7 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -718,13 +700,13 @@
       <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="1" t="s">
         <v>40</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -750,31 +732,31 @@
       <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3">
         <v>0.72633076346381631</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3">
-        <v>0.41779646230124612</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0.41779646230124612</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0.4000846590633545</v>
-      </c>
-      <c r="J3" s="17">
-        <v>0.1821188786353993</v>
+        <v>0.44523906042508188</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.26571043968282843</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.44523906042508188</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.2890504998920897</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="10">
         <v>0.58507962712671024</v>
       </c>
       <c r="M3" s="7" t="s">
@@ -794,7 +776,7 @@
       <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="3">
@@ -804,21 +786,21 @@
         <v>8</v>
       </c>
       <c r="G4" s="3">
-        <v>0.57002409575526458</v>
-      </c>
-      <c r="H4" s="16">
-        <v>0.57002409575526458</v>
-      </c>
-      <c r="I4" s="16">
-        <v>0.25844769102402221</v>
-      </c>
-      <c r="J4" s="17">
-        <v>0.17152821322071329</v>
+        <v>0.61486694648219375</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.61486694648219375</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.18355637643305581</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.20157667708475041</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="10">
         <v>0.55236031228573046</v>
       </c>
       <c r="M4" s="7" t="s">
@@ -838,31 +820,31 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="3">
-        <v>0.74557114854930751</v>
+        <v>0.74557114854930762</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="3">
-        <v>0.48455759982842</v>
-      </c>
-      <c r="H5" s="16">
-        <v>0.41147603968855212</v>
-      </c>
-      <c r="I5" s="16">
-        <v>0.48455759982842</v>
-      </c>
-      <c r="J5" s="17">
-        <v>0.1039663604830279</v>
+        <v>0.55916177072649531</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.32949059936103042</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.55916177072649531</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.11134762991247429</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="10">
         <v>0.57726191012009487</v>
       </c>
       <c r="M5" s="7" t="s">
@@ -882,7 +864,7 @@
       <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3">
@@ -892,21 +874,21 @@
         <v>8</v>
       </c>
       <c r="G6" s="3">
-        <v>0.5787481150693905</v>
-      </c>
-      <c r="H6" s="16">
-        <v>0.5787481150693905</v>
-      </c>
-      <c r="I6" s="16">
-        <v>0.26650029803927933</v>
-      </c>
-      <c r="J6" s="17">
-        <v>0.15475158689133031</v>
+        <v>0.64293810985264055</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.64293810985264055</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.20929925675213101</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.14776263339522841</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="10">
         <v>0.54153527244196309</v>
       </c>
       <c r="M6" s="7" t="s">
@@ -926,31 +908,31 @@
       <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="3">
         <v>0.56680960799109492</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="G7" s="3">
-        <v>0.53965320878892376</v>
-      </c>
-      <c r="H7" s="16">
-        <v>0.53965320878892376</v>
-      </c>
-      <c r="I7" s="16">
-        <v>0.16154110435959401</v>
-      </c>
-      <c r="J7" s="17">
-        <v>0.29880568685148229</v>
+        <v>0.49805029943582008</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.40024588935636513</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.1017038112078148</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.49805029943582008</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="10">
         <v>0.5206442695273158</v>
       </c>
       <c r="M7" s="7" t="s">
@@ -970,7 +952,7 @@
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="3">
@@ -980,21 +962,21 @@
         <v>8</v>
       </c>
       <c r="G8" s="3">
-        <v>0.46807533244096289</v>
-      </c>
-      <c r="H8" s="16">
-        <v>0.46807533244096289</v>
-      </c>
-      <c r="I8" s="16">
-        <v>0.39081062829674401</v>
-      </c>
-      <c r="J8" s="17">
-        <v>0.14111403926229321</v>
+        <v>0.4038677373657697</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.4038677373657697</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.38111220776314281</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.2150200548710875</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="10">
         <v>0.57036701856795147</v>
       </c>
       <c r="M8" s="7" t="s">
@@ -1014,7 +996,7 @@
       <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="3">
@@ -1024,21 +1006,21 @@
         <v>8</v>
       </c>
       <c r="G9" s="3">
-        <v>0.54386814242205095</v>
-      </c>
-      <c r="H9" s="16">
-        <v>0.54386814242205095</v>
-      </c>
-      <c r="I9" s="16">
-        <v>0.34725872550447062</v>
-      </c>
-      <c r="J9" s="17">
-        <v>0.1088731320734785</v>
+        <v>0.6032569355684273</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.6032569355684273</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.27138594830148549</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.12535711613008721</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="10">
         <v>0.55213357416946263</v>
       </c>
       <c r="M9" s="7" t="s">
@@ -1058,7 +1040,7 @@
       <c r="C10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="3">
@@ -1068,21 +1050,21 @@
         <v>8</v>
       </c>
       <c r="G10" s="3">
-        <v>0.66479288740316855</v>
-      </c>
-      <c r="H10" s="16">
-        <v>0.66479288740316855</v>
-      </c>
-      <c r="I10" s="16">
-        <v>0.19650377027372881</v>
-      </c>
-      <c r="J10" s="17">
-        <v>0.1387033423231028</v>
+        <v>0.7781246925925831</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.7781246925925831</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.12615590062251519</v>
+      </c>
+      <c r="J10" s="3">
+        <v>9.5719406784901803E-2</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="10">
         <v>0.61800500937999048</v>
       </c>
       <c r="M10" s="7" t="s">
@@ -1102,7 +1084,7 @@
       <c r="C11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="3">
@@ -1112,21 +1094,21 @@
         <v>8</v>
       </c>
       <c r="G11" s="3">
-        <v>0.67285247674920923</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.67285247674920923</v>
-      </c>
-      <c r="I11" s="16">
-        <v>0.16801189657963531</v>
-      </c>
-      <c r="J11" s="17">
-        <v>0.15913562667115561</v>
+        <v>0.75165613929899011</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.75165613929899011</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.1056179321210461</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.14272592857996391</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="10">
         <v>0.56495442307833654</v>
       </c>
       <c r="M11" s="7" t="s">
@@ -1146,7 +1128,7 @@
       <c r="C12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="3">
@@ -1156,21 +1138,21 @@
         <v>8</v>
       </c>
       <c r="G12" s="3">
-        <v>0.55407562634678231</v>
-      </c>
-      <c r="H12" s="16">
-        <v>0.55407562634678231</v>
-      </c>
-      <c r="I12" s="16">
-        <v>0.1870284866100306</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0.25889588704318711</v>
+        <v>0.5367143169986861</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.5367143169986861</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.1549960544669611</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.30828962853435288</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="10">
         <v>0.55532067109467609</v>
       </c>
       <c r="M12" s="7" t="s">
@@ -1272,7 +1254,7 @@
         <v>0.11134762991247429</v>
       </c>
     </row>
-    <row r="17" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1295,7 +1277,7 @@
         <v>0.14776263339522841</v>
       </c>
     </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D18" s="2" t="s">
         <v>19</v>
       </c>
@@ -1318,7 +1300,7 @@
         <v>0.49805029943582008</v>
       </c>
     </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
         <v>21</v>
       </c>
@@ -1341,7 +1323,7 @@
         <v>0.2150200548710875</v>
       </c>
     </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D20" s="2" t="s">
         <v>24</v>
       </c>
@@ -1364,7 +1346,7 @@
         <v>0.12535711613008721</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
         <v>27</v>
       </c>
@@ -1387,7 +1369,7 @@
         <v>9.5719406784901803E-2</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
         <v>31</v>
       </c>
@@ -1410,7 +1392,7 @@
         <v>0.14272592857996391</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
         <v>32</v>
       </c>
@@ -1432,6 +1414,76 @@
       <c r="J23" s="3">
         <v>0.30828962853435288</v>
       </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="H29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="H30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="H31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="H32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+    </row>
+    <row r="33" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+    </row>
+    <row r="34" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+    </row>
+    <row r="36" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+    </row>
+    <row r="37" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+    </row>
+    <row r="38" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Predictions/2026-04-18.xlsx
+++ b/Predictions/2026-04-18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFF11CE-8840-4C95-9FD7-C7F793E31535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6ECE5AB-74F1-4096-9AAA-8D632D979052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
   <si>
     <t>Red Corner</t>
   </si>
@@ -103,15 +103,6 @@
     <t>Women's Bantamweight</t>
   </si>
   <si>
-    <t>Mitch Raposo</t>
-  </si>
-  <si>
-    <t>Allan Nascimento</t>
-  </si>
-  <si>
-    <t>Flyweight</t>
-  </si>
-  <si>
     <t>JJ Aldrich</t>
   </si>
   <si>
@@ -146,9 +137,6 @@
   </si>
   <si>
     <t>Old Model</t>
-  </si>
-  <si>
-    <t>Submission</t>
   </si>
 </sst>
 </file>
@@ -195,7 +183,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -292,11 +280,177 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -337,6 +491,57 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -660,21 +865,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D1" s="12" t="s">
-        <v>37</v>
+      <c r="D1" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="12" t="s">
-        <v>41</v>
+      <c r="J1" s="25"/>
+      <c r="K1" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="L1" s="14"/>
       <c r="M1" s="12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N1" s="14"/>
     </row>
@@ -688,35 +893,35 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>34</v>
+      <c r="D2" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>3</v>
@@ -732,28 +937,28 @@
       <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="28" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3">
-        <v>0.72633076346381631</v>
+        <v>0.72262345805072037</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="3">
-        <v>0.44523906042508188</v>
+        <v>0.46881479893066991</v>
       </c>
       <c r="H3" s="3">
-        <v>0.26571043968282843</v>
+        <v>0.3002394439659018</v>
       </c>
       <c r="I3" s="3">
-        <v>0.44523906042508188</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0.2890504998920897</v>
-      </c>
-      <c r="K3" s="2" t="s">
+        <v>0.46881479893066991</v>
+      </c>
+      <c r="J3" s="29">
+        <v>0.2309457571034283</v>
+      </c>
+      <c r="K3" s="22" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="10">
@@ -776,28 +981,28 @@
       <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="28" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="3">
-        <v>0.6093470816544958</v>
+        <v>0.57901563301901415</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="3">
-        <v>0.61486694648219375</v>
+        <v>0.44842107401794429</v>
       </c>
       <c r="H4" s="3">
-        <v>0.61486694648219375</v>
+        <v>0.44842107401794429</v>
       </c>
       <c r="I4" s="3">
-        <v>0.18355637643305581</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0.20157667708475041</v>
-      </c>
-      <c r="K4" s="2" t="s">
+        <v>0.29918784725393172</v>
+      </c>
+      <c r="J4" s="29">
+        <v>0.25239107872812411</v>
+      </c>
+      <c r="K4" s="22" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="10">
@@ -820,28 +1025,28 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="28" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="3">
-        <v>0.74557114854930762</v>
+        <v>0.72666306736921149</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="3">
-        <v>0.55916177072649531</v>
+        <v>0.47193141512061798</v>
       </c>
       <c r="H5" s="3">
-        <v>0.32949059936103042</v>
+        <v>0.36877739940137788</v>
       </c>
       <c r="I5" s="3">
-        <v>0.55916177072649531</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.11134762991247429</v>
-      </c>
-      <c r="K5" s="2" t="s">
+        <v>0.47193141512061798</v>
+      </c>
+      <c r="J5" s="29">
+        <v>0.15929118547800411</v>
+      </c>
+      <c r="K5" s="22" t="s">
         <v>13</v>
       </c>
       <c r="L5" s="10">
@@ -864,28 +1069,28 @@
       <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="28" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3">
-        <v>0.57904156763755621</v>
+        <v>0.5923278399789782</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="3">
-        <v>0.64293810985264055</v>
+        <v>0.53434971535753051</v>
       </c>
       <c r="H6" s="3">
-        <v>0.64293810985264055</v>
+        <v>0.53434971535753051</v>
       </c>
       <c r="I6" s="3">
-        <v>0.20929925675213101</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.14776263339522841</v>
-      </c>
-      <c r="K6" s="2" t="s">
+        <v>0.27751904808588018</v>
+      </c>
+      <c r="J6" s="29">
+        <v>0.18813123655658939</v>
+      </c>
+      <c r="K6" s="22" t="s">
         <v>16</v>
       </c>
       <c r="L6" s="10">
@@ -908,28 +1113,28 @@
       <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="28" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="3">
-        <v>0.56680960799109492</v>
+        <v>0.56656823576215165</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3">
-        <v>0.49805029943582008</v>
+        <v>0.41946847352738448</v>
       </c>
       <c r="H7" s="3">
-        <v>0.40024588935636513</v>
+        <v>0.41946847352738448</v>
       </c>
       <c r="I7" s="3">
-        <v>0.1017038112078148</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.49805029943582008</v>
-      </c>
-      <c r="K7" s="2" t="s">
+        <v>0.21488670568714599</v>
+      </c>
+      <c r="J7" s="29">
+        <v>0.3656448207854695</v>
+      </c>
+      <c r="K7" s="22" t="s">
         <v>19</v>
       </c>
       <c r="L7" s="10">
@@ -952,28 +1157,28 @@
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="28" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="3">
-        <v>0.51437123342106628</v>
+        <v>0.50140831292591292</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3">
-        <v>0.4038677373657697</v>
+        <v>0.4034698581529681</v>
       </c>
       <c r="H8" s="3">
-        <v>0.4038677373657697</v>
+        <v>0.38792373041708811</v>
       </c>
       <c r="I8" s="3">
-        <v>0.38111220776314281</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.2150200548710875</v>
-      </c>
-      <c r="K8" s="2" t="s">
+        <v>0.4034698581529681</v>
+      </c>
+      <c r="J8" s="29">
+        <v>0.20860641142994371</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="10">
@@ -996,28 +1201,28 @@
       <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
+      <c r="D9" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>0.50437397780926208</v>
+        <v>0.50318625241944936</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="3">
-        <v>0.6032569355684273</v>
+        <v>0.50723671552945437</v>
       </c>
       <c r="H9" s="3">
-        <v>0.6032569355684273</v>
+        <v>0.50723671552945437</v>
       </c>
       <c r="I9" s="3">
-        <v>0.27138594830148549</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.12535711613008721</v>
-      </c>
-      <c r="K9" s="2" t="s">
+        <v>0.3090391505592302</v>
+      </c>
+      <c r="J9" s="29">
+        <v>0.18372413391131551</v>
+      </c>
+      <c r="K9" s="22" t="s">
         <v>25</v>
       </c>
       <c r="L9" s="10">
@@ -1038,405 +1243,115 @@
         <v>28</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>28</v>
       </c>
       <c r="E10" s="3">
-        <v>0.5629022447616322</v>
+        <v>0.508718310285459</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="3">
-        <v>0.7781246925925831</v>
+        <v>0.55766158029356616</v>
       </c>
       <c r="H10" s="3">
-        <v>0.7781246925925831</v>
+        <v>0.55766158029356616</v>
       </c>
       <c r="I10" s="3">
-        <v>0.12615590062251519</v>
-      </c>
-      <c r="J10" s="3">
-        <v>9.5719406784901803E-2</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>28</v>
+        <v>0.25521672562135772</v>
+      </c>
+      <c r="J10" s="29">
+        <v>0.1871216940850762</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>27</v>
       </c>
       <c r="L10" s="10">
-        <v>0.61800500937999048</v>
+        <v>0.56495442307833654</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>28</v>
       </c>
       <c r="N10" s="8">
-        <v>0.74145832088746899</v>
+        <v>0.51582762236944391</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0.50330741055311812</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="C11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0.53117529916980721</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="3">
-        <v>0.75165613929899011</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.75165613929899011</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.1056179321210461</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.14272592857996391</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0.56495442307833654</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0.51582762236944391</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0.51137475212665351</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.5367143169986861</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.5367143169986861</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0.1549960544669611</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0.30828962853435288</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="10">
+      <c r="G11" s="16">
+        <v>0.46180222001196458</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0.46180222001196458</v>
+      </c>
+      <c r="I11" s="16">
+        <v>0.2354571399123066</v>
+      </c>
+      <c r="J11" s="31">
+        <v>0.30274064007572871</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="17">
         <v>0.55532067109467609</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="8">
+      <c r="M11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="19">
         <v>0.68077962743839049</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0.72633076346381631</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.44523906042508188</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.26571043968282843</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0.44523906042508188</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0.2890504998920897</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.6093470816544958</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.61486694648219375</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.61486694648219375</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0.18355637643305581</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0.20157667708475041</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0.74557114854930762</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0.55916177072649531</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.32949059936103042</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0.55916177072649531</v>
-      </c>
-      <c r="J16" s="3">
-        <v>0.11134762991247429</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.57904156763755621</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0.64293810985264055</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.64293810985264055</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.20929925675213101</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0.14776263339522841</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0.56680960799109492</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0.49805029943582008</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.40024588935636513</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0.1017038112078148</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0.49805029943582008</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0.51437123342106628</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.4038677373657697</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.4038677373657697</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.38111220776314281</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.2150200548710875</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0.50437397780926208</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0.6032569355684273</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.6032569355684273</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0.27138594830148549</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0.12535711613008721</v>
-      </c>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.5629022447616322</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0.7781246925925831</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0.7781246925925831</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0.12615590062251519</v>
-      </c>
-      <c r="J21" s="3">
-        <v>9.5719406784901803E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0.50330741055311812</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0.75165613929899011</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0.75165613929899011</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0.1056179321210461</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0.14272592857996391</v>
-      </c>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0.51137475212665351</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0.5367143169986861</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0.5367143169986861</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0.1549960544669611</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0.30828962853435288</v>
-      </c>
-    </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H29" s="11"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
     </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
     </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
-    <row r="32" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -1477,13 +1392,6 @@
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
-    </row>
-    <row r="38" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Predictions/2026-04-18.xlsx
+++ b/Predictions/2026-04-18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6ECE5AB-74F1-4096-9AAA-8D632D979052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D2CA53-D5D4-44B6-A2EC-5B71409348F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
   <si>
     <t>Red Corner</t>
   </si>
@@ -137,6 +137,39 @@
   </si>
   <si>
     <t>Old Model</t>
+  </si>
+  <si>
+    <t>Submission</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">John Castaneda </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Draw)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jamey-Lyn Horth </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Robbery)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -146,7 +179,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,8 +201,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,6 +222,12 @@
         <bgColor rgb="FFD3D3D3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="20">
     <border>
@@ -450,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -483,64 +529,88 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -851,7 +921,7 @@
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
@@ -865,23 +935,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="13" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="12" t="s">
+      <c r="L1" s="31"/>
+      <c r="M1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="14"/>
+      <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -893,7 +963,7 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="21" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -911,10 +981,10 @@
       <c r="I2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="18" t="s">
         <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -937,37 +1007,37 @@
       <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="3">
-        <v>0.72262345805072037</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="37">
+        <v>0.73</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3">
-        <v>0.46881479893066991</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.3002394439659018</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.46881479893066991</v>
-      </c>
-      <c r="J3" s="29">
-        <v>0.2309457571034283</v>
-      </c>
-      <c r="K3" s="22" t="s">
+      <c r="G3" s="37">
+        <v>0.441</v>
+      </c>
+      <c r="H3" s="37">
+        <v>0.31</v>
+      </c>
+      <c r="I3" s="37">
+        <v>0.441</v>
+      </c>
+      <c r="J3" s="39">
+        <v>0.249</v>
+      </c>
+      <c r="K3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="33">
         <v>0.58507962712671024</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="35">
         <v>0.53724954619042453</v>
       </c>
     </row>
@@ -981,28 +1051,28 @@
       <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3">
-        <v>0.57901563301901415</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="37">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="3">
-        <v>0.44842107401794429</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.44842107401794429</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.29918784725393172</v>
-      </c>
-      <c r="J4" s="29">
-        <v>0.25239107872812411</v>
-      </c>
-      <c r="K4" s="22" t="s">
+      <c r="G4" s="37">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="H4" s="37">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="I4" s="37">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="J4" s="39">
+        <v>0.27</v>
+      </c>
+      <c r="K4" s="19" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="10">
@@ -1025,31 +1095,31 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="23" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="3">
-        <v>0.72666306736921149</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="3">
-        <v>0.47193141512061798</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="H5" s="3">
-        <v>0.36877739940137788</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="I5" s="3">
-        <v>0.47193141512061798</v>
-      </c>
-      <c r="J5" s="29">
-        <v>0.15929118547800411</v>
-      </c>
-      <c r="K5" s="22" t="s">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0.158</v>
+      </c>
+      <c r="K5" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="33">
         <v>0.57726191012009487</v>
       </c>
       <c r="M5" s="7" t="s">
@@ -1069,37 +1139,37 @@
       <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="3">
-        <v>0.5923278399789782</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="37">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="F6" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="3">
-        <v>0.53434971535753051</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.53434971535753051</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.27751904808588018</v>
-      </c>
-      <c r="J6" s="29">
-        <v>0.18813123655658939</v>
-      </c>
-      <c r="K6" s="22" t="s">
+      <c r="G6" s="37">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="H6" s="37">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="I6" s="37">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="J6" s="39">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="K6" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="33">
         <v>0.54153527244196309</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="35">
         <v>0.52246509063124191</v>
       </c>
     </row>
@@ -1113,28 +1183,28 @@
       <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="23" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="3">
-        <v>0.56656823576215165</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3">
-        <v>0.41946847352738448</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="H7" s="3">
-        <v>0.41946847352738448</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="I7" s="3">
-        <v>0.21488670568714599</v>
-      </c>
-      <c r="J7" s="29">
-        <v>0.3656448207854695</v>
-      </c>
-      <c r="K7" s="22" t="s">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="K7" s="19" t="s">
         <v>19</v>
       </c>
       <c r="L7" s="10">
@@ -1157,37 +1227,37 @@
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="23" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="3">
-        <v>0.50140831292591292</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="3">
-        <v>0.4034698581529681</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="H8" s="3">
-        <v>0.38792373041708811</v>
+        <v>0.38</v>
       </c>
       <c r="I8" s="3">
-        <v>0.4034698581529681</v>
-      </c>
-      <c r="J8" s="29">
-        <v>0.20860641142994371</v>
-      </c>
-      <c r="K8" s="22" t="s">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J8" s="24">
+        <v>0.221</v>
+      </c>
+      <c r="K8" s="19" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="10">
         <v>0.57036701856795147</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="35">
         <v>0.64140582314118721</v>
       </c>
     </row>
@@ -1201,28 +1271,28 @@
       <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="23" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>0.50318625241944936</v>
+        <v>0.52</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="3">
-        <v>0.50723671552945437</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="H9" s="3">
-        <v>0.50723671552945437</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="I9" s="3">
-        <v>0.3090391505592302</v>
-      </c>
-      <c r="J9" s="29">
-        <v>0.18372413391131551</v>
-      </c>
-      <c r="K9" s="22" t="s">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="J9" s="24">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="K9" s="19" t="s">
         <v>25</v>
       </c>
       <c r="L9" s="10">
@@ -1245,31 +1315,31 @@
       <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>28</v>
+      <c r="D10" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="E10" s="3">
-        <v>0.508718310285459</v>
+        <v>0.502</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="3">
-        <v>0.55766158029356616</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="H10" s="3">
-        <v>0.55766158029356616</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="I10" s="3">
-        <v>0.25521672562135772</v>
-      </c>
-      <c r="J10" s="29">
-        <v>0.1871216940850762</v>
-      </c>
-      <c r="K10" s="22" t="s">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="J10" s="24">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="K10" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="33">
         <v>0.56495442307833654</v>
       </c>
       <c r="M10" s="7" t="s">
@@ -1280,46 +1350,46 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="I11" s="13">
+        <v>0.214</v>
+      </c>
+      <c r="J11" s="26">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="K11" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="16">
-        <v>0.53117529916980721</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="16">
-        <v>0.46180222001196458</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.46180222001196458</v>
-      </c>
-      <c r="I11" s="16">
-        <v>0.2354571399123066</v>
-      </c>
-      <c r="J11" s="31">
-        <v>0.30274064007572871</v>
-      </c>
-      <c r="K11" s="23" t="s">
+      <c r="L11" s="14">
+        <v>0.55532067109467609</v>
+      </c>
+      <c r="M11" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="17">
-        <v>0.55532067109467609</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="19">
+      <c r="N11" s="16">
         <v>0.68077962743839049</v>
       </c>
     </row>

--- a/Predictions/2026-04-18.xlsx
+++ b/Predictions/2026-04-18.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D2CA53-D5D4-44B6-A2EC-5B71409348F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937F7AAA-84B4-482E-8814-90DABB4FE5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t>Red Corner</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>SUB %</t>
-  </si>
-  <si>
-    <t>Old Model</t>
   </si>
   <si>
     <t>Submission</t>
@@ -229,7 +226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -376,32 +373,6 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -496,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -525,9 +496,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -535,9 +503,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -547,19 +512,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -568,19 +530,31 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -588,30 +562,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -915,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -929,31 +879,25 @@
     <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D1" s="27" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D1" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="30" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="31"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L1" s="32"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -963,7 +907,7 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="16" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -981,23 +925,17 @@
       <c r="I2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1007,41 +945,35 @@
       <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="25">
         <v>0.73</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="37">
+      <c r="G3" s="25">
         <v>0.441</v>
       </c>
-      <c r="H3" s="37">
+      <c r="H3" s="25">
         <v>0.31</v>
       </c>
-      <c r="I3" s="37">
+      <c r="I3" s="25">
         <v>0.441</v>
       </c>
-      <c r="J3" s="39">
+      <c r="J3" s="27">
         <v>0.249</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="33">
-        <v>0.58507962712671024</v>
-      </c>
-      <c r="M3" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="N3" s="35">
+      <c r="L3" s="23">
         <v>0.53724954619042453</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1051,41 +983,35 @@
       <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="25">
         <v>0.59099999999999997</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="37">
+      <c r="G4" s="25">
         <v>0.40899999999999997</v>
       </c>
-      <c r="H4" s="37">
+      <c r="H4" s="25">
         <v>0.40899999999999997</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="25">
         <v>0.32100000000000001</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="27">
         <v>0.27</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="10">
-        <v>0.55236031228573046</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="8">
+      <c r="L4" s="8">
         <v>0.56008091750145383</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1095,7 +1021,7 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="3">
@@ -1113,23 +1039,17 @@
       <c r="I5" s="3">
         <v>0.48699999999999999</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="19">
         <v>0.158</v>
       </c>
-      <c r="K5" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="33">
-        <v>0.57726191012009487</v>
-      </c>
-      <c r="M5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="8">
+      <c r="L5" s="8">
         <v>0.58823704302014712</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1139,41 +1059,35 @@
       <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="25">
         <v>0.60499999999999998</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="25">
         <v>0.52400000000000002</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="25">
         <v>0.52400000000000002</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="25">
         <v>0.29899999999999999</v>
       </c>
-      <c r="J6" s="39">
+      <c r="J6" s="27">
         <v>0.17699999999999999</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="33">
-        <v>0.54153527244196309</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="35">
+      <c r="L6" s="23">
         <v>0.52246509063124191</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -1183,14 +1097,14 @@
       <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="3">
         <v>0.56499999999999995</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" s="3">
         <v>0.42599999999999999</v>
@@ -1201,23 +1115,17 @@
       <c r="I7" s="3">
         <v>0.17100000000000001</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="19">
         <v>0.42599999999999999</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="10">
-        <v>0.5206442695273158</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="8">
+      <c r="L7" s="8">
         <v>0.66567702703587706</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1227,7 +1135,7 @@
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="3">
@@ -1245,23 +1153,17 @@
       <c r="I8" s="3">
         <v>0.39900000000000002</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="19">
         <v>0.221</v>
       </c>
-      <c r="K8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0.57036701856795147</v>
-      </c>
-      <c r="M8" s="34" t="s">
+      <c r="K8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="35">
+      <c r="L8" s="23">
         <v>0.64140582314118721</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1271,7 +1173,7 @@
       <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="18" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="3">
@@ -1289,23 +1191,17 @@
       <c r="I9" s="3">
         <v>0.32400000000000001</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="19">
         <v>0.19700000000000001</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="10">
-        <v>0.55213357416946263</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="8">
+      <c r="L9" s="8">
         <v>0.5063976391063858</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1315,8 +1211,8 @@
       <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>41</v>
+      <c r="D10" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="E10" s="3">
         <v>0.502</v>
@@ -1333,140 +1229,107 @@
       <c r="I10" s="3">
         <v>0.23799999999999999</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="19">
         <v>0.21299999999999999</v>
       </c>
-      <c r="K10" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="33">
-        <v>0.56495442307833654</v>
-      </c>
-      <c r="M10" s="7" t="s">
+      <c r="K10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N10" s="8">
+      <c r="L10" s="8">
         <v>0.51582762236944391</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="D11" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="12">
         <v>0.50600000000000001</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>0.44800000000000001</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>0.44800000000000001</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <v>0.214</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="21">
         <v>0.33800000000000002</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="13" t="s">
         <v>29</v>
       </c>
       <c r="L11" s="14">
-        <v>0.55532067109467609</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="16">
         <v>0.68077962743839049</v>
       </c>
     </row>
-    <row r="28" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-    </row>
-    <row r="29" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-    </row>
-    <row r="30" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-    </row>
-    <row r="31" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-    </row>
-    <row r="32" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-    </row>
-    <row r="33" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-    </row>
-    <row r="34" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-    </row>
-    <row r="35" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-    </row>
-    <row r="36" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-    </row>
-    <row r="37" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
+    <row r="28" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+    </row>
+    <row r="29" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+    </row>
+    <row r="31" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+    </row>
+    <row r="32" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+    </row>
+    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+    </row>
+    <row r="34" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+    </row>
+    <row r="35" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+    </row>
+    <row r="36" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+    </row>
+    <row r="37" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="D1:J1"/>
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
